--- a/agent_runs/manjidiwang/episodes/ep29/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep29/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>大堂败局（，总时长：11秒，镜头数：5个）</t>
+          <t>大堂败局</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>押离与收束（，总时长：10秒，镜头数：4个）</t>
+          <t>押离与收束</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>病房转危（，总时长：10秒，镜头数：4个）</t>
+          <t>病房转危</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>交托家业（，总时长：10秒，镜头数：4个）</t>
+          <t>交托家业</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
